--- a/artfynd/A 19812-2024 artfynd.xlsx
+++ b/artfynd/A 19812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744055</v>
+        <v>122744053</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lomsjön N, Ång</t>
+          <t>Sörmlandsleden S, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673200</v>
+        <v>673197</v>
       </c>
       <c r="R2" t="n">
-        <v>7074312</v>
+        <v>7074052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744053</v>
+        <v>122744054</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden S, Ång</t>
+          <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673197</v>
+        <v>673172</v>
       </c>
       <c r="R3" t="n">
-        <v>7074052</v>
+        <v>7074370</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744054</v>
+        <v>122744055</v>
       </c>
       <c r="B4" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,34 +903,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673172</v>
+        <v>673200</v>
       </c>
       <c r="R4" t="n">
-        <v>7074370</v>
+        <v>7074312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 19812-2024 artfynd.xlsx
+++ b/artfynd/A 19812-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744053</v>
+        <v>122744054</v>
       </c>
       <c r="B2" t="n">
         <v>90962</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden S, Ång</t>
+          <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673197</v>
+        <v>673172</v>
       </c>
       <c r="R2" t="n">
-        <v>7074052</v>
+        <v>7074370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744054</v>
+        <v>122744053</v>
       </c>
       <c r="B3" t="n">
         <v>90962</v>
@@ -817,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lomsjön N, Ång</t>
+          <t>Sörmlandsleden S, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673172</v>
+        <v>673197</v>
       </c>
       <c r="R3" t="n">
-        <v>7074370</v>
+        <v>7074052</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 19812-2024 artfynd.xlsx
+++ b/artfynd/A 19812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744054</v>
+        <v>122744055</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673172</v>
+        <v>673200</v>
       </c>
       <c r="R2" t="n">
-        <v>7074370</v>
+        <v>7074312</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744055</v>
+        <v>122744054</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,38 +907,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673200</v>
+        <v>673172</v>
       </c>
       <c r="R4" t="n">
-        <v>7074312</v>
+        <v>7074370</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 19812-2024 artfynd.xlsx
+++ b/artfynd/A 19812-2024 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744053</v>
+        <v>122744054</v>
       </c>
       <c r="B3" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,14 +821,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden S, Ång</t>
+          <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673197</v>
+        <v>673172</v>
       </c>
       <c r="R3" t="n">
-        <v>7074052</v>
+        <v>7074370</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744054</v>
+        <v>122744053</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,14 +927,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomsjön N, Ång</t>
+          <t>Sörmlandsleden S, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673172</v>
+        <v>673197</v>
       </c>
       <c r="R4" t="n">
-        <v>7074370</v>
+        <v>7074052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 19812-2024 artfynd.xlsx
+++ b/artfynd/A 19812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744055</v>
+        <v>122744054</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673200</v>
+        <v>673172</v>
       </c>
       <c r="R2" t="n">
-        <v>7074312</v>
+        <v>7074370</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -774,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -785,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744054</v>
+        <v>122744053</v>
       </c>
       <c r="B3" t="n">
         <v>90970</v>
@@ -821,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lomsjön N, Ång</t>
+          <t>Sörmlandsleden S, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673172</v>
+        <v>673197</v>
       </c>
       <c r="R3" t="n">
-        <v>7074370</v>
+        <v>7074052</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744053</v>
+        <v>122744055</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,34 +903,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden S, Ång</t>
+          <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673197</v>
+        <v>673200</v>
       </c>
       <c r="R4" t="n">
-        <v>7074052</v>
+        <v>7074312</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 19812-2024 artfynd.xlsx
+++ b/artfynd/A 19812-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744053</v>
+        <v>122744055</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörmlandsleden S, Ång</t>
+          <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673197</v>
+        <v>673200</v>
       </c>
       <c r="R3" t="n">
-        <v>7074052</v>
+        <v>7074312</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744055</v>
+        <v>122744053</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,38 +907,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomsjön N, Ång</t>
+          <t>Sörmlandsleden S, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673200</v>
+        <v>673197</v>
       </c>
       <c r="R4" t="n">
-        <v>7074312</v>
+        <v>7074052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 19812-2024 artfynd.xlsx
+++ b/artfynd/A 19812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744054</v>
+        <v>122744053</v>
       </c>
       <c r="B2" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lomsjön N, Ång</t>
+          <t>Sörmlandsleden S, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673172</v>
+        <v>673197</v>
       </c>
       <c r="R2" t="n">
-        <v>7074370</v>
+        <v>7074052</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>122744055</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744053</v>
+        <v>122744054</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>90973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,14 +927,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sörmlandsleden S, Ång</t>
+          <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673197</v>
+        <v>673172</v>
       </c>
       <c r="R4" t="n">
-        <v>7074052</v>
+        <v>7074370</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 19812-2024 artfynd.xlsx
+++ b/artfynd/A 19812-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122744053</v>
+        <v>122744055</v>
       </c>
       <c r="B2" t="n">
-        <v>90973</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörmlandsleden S, Ång</t>
+          <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>673197</v>
+        <v>673200</v>
       </c>
       <c r="R2" t="n">
-        <v>7074052</v>
+        <v>7074312</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122744055</v>
+        <v>122744054</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,38 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lomsjön N, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>673200</v>
+        <v>673172</v>
       </c>
       <c r="R3" t="n">
-        <v>7074312</v>
+        <v>7074370</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122744054</v>
+        <v>122744053</v>
       </c>
       <c r="B4" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,14 +927,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomsjön N, Ång</t>
+          <t>Sörmlandsleden S, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>673172</v>
+        <v>673197</v>
       </c>
       <c r="R4" t="n">
-        <v>7074370</v>
+        <v>7074052</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
